--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_138_R14.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_138_R14.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6544</v>
+        <v>4.9641</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9763</v>
+        <v>3.7901</v>
       </c>
       <c r="F2" t="n">
-        <v>1.678</v>
+        <v>1.1739</v>
       </c>
       <c r="G2" t="n">
         <v>2.0433</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0848</v>
+        <v>0.2249</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7468</v>
+        <v>0.067</v>
       </c>
       <c r="U2" t="n">
-        <v>0.662</v>
+        <v>0.1579</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7068</v>
+        <v>3.1752</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0645</v>
+        <v>1.6674</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6423</v>
+        <v>1.5079</v>
       </c>
       <c r="G3" t="n">
         <v>1.8374</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0859</v>
+        <v>0.5544</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5272</v>
+        <v>0.13</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5588</v>
+        <v>0.4244</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0722</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9438</v>
+        <v>3.0296</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4325</v>
+        <v>1.4587</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5112</v>
+        <v>1.571</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8287</v>
+        <v>0.5139</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5175</v>
+        <v>1.1966</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3113</v>
+        <v>-0.6827</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3614</v>
+        <v>1.015</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6253</v>
+        <v>2.4808</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7361</v>
+        <v>-1.4658</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5326</v>
+        <v>-0.5011</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1078</v>
+        <v>-1.2842</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4248</v>
+        <v>0.7831</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3195</v>
+        <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2415</v>
+        <v>-0.7136</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3031</v>
+        <v>-0.3064</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9384</v>
+        <v>-0.4072</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.214</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.214</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9544</v>
+        <v>2.233</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7195</v>
+        <v>1.2594</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2349</v>
+        <v>0.9735</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5139</v>
+        <v>0.8287</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1966</v>
+        <v>0.5175</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6827</v>
+        <v>0.3113</v>
       </c>
       <c r="J5" t="n">
-        <v>1.015</v>
+        <v>1.3614</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4808</v>
+        <v>0.6253</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.4658</v>
+        <v>0.7361</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5011</v>
+        <v>-0.5326</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2842</v>
+        <v>-0.1078</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7831</v>
+        <v>-0.4248</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0154</v>
+        <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7888</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0455</v>
+        <v>0.13</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7433</v>
+        <v>0.4007</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6778999999999999</v>
+        <v>-1.214</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1797</v>
+        <v>1.4538</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9928</v>
+        <v>-1.8867</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1725</v>
+        <v>3.3405</v>
       </c>
       <c r="G6" t="n">
         <v>1.7478</v>
@@ -922,13 +922,13 @@
         <v>3.4793</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2025</v>
+        <v>0.4766</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1537</v>
+        <v>0.2598</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0488</v>
+        <v>0.2168</v>
       </c>
       <c r="V6" t="n">
         <v>-1.4665</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7776999999999999</v>
+        <v>1.2663</v>
       </c>
       <c r="E7" t="n">
-        <v>0.732</v>
+        <v>-1.0092</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0457</v>
+        <v>2.2755</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3871</v>
+        <v>0.4132</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8656</v>
+        <v>1.3939</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4785</v>
+        <v>-0.9807</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9165</v>
+        <v>0.335</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4452</v>
+        <v>1.6805</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-1.3455</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5294</v>
+        <v>0.0781</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5796</v>
+        <v>-0.2866</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0502</v>
+        <v>0.3648</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6225000000000001</v>
+        <v>-0.0747</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9752</v>
+        <v>0.0474</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3528</v>
+        <v>-0.1221</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0955</v>
+        <v>0.4471</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1022</v>
+        <v>0.099</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0067</v>
+        <v>0.3481</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4132</v>
+        <v>0.3871</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3939</v>
+        <v>0.8656</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9807</v>
+        <v>-0.4785</v>
       </c>
       <c r="J8" t="n">
-        <v>0.335</v>
+        <v>0.9165</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6805</v>
+        <v>1.4452</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3455</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0781</v>
+        <v>-0.5294</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2866</v>
+        <v>-0.5796</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3648</v>
+        <v>0.0502</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.9278</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.3917</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.3195</v>
-      </c>
       <c r="S8" t="n">
-        <v>-1.4365</v>
+        <v>0.2919</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0455</v>
+        <v>0.3422</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.391</v>
+        <v>-0.0503</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7993</v>
+        <v>-0.311</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2687</v>
+        <v>-0.9149</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4694</v>
+        <v>0.6039</v>
       </c>
       <c r="G10" t="n">
         <v>0.0442</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1502</v>
+        <v>0.338</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3734</v>
+        <v>-0.0196</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2232</v>
+        <v>0.3576</v>
       </c>
       <c r="V10" t="n">
         <v>0.9304</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7628</v>
+        <v>-2.1667</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0549</v>
+        <v>-1.2908</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7079</v>
+        <v>-0.8759</v>
       </c>
       <c r="G11" t="n">
         <v>0.504</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7332</v>
+        <v>0.3293</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4129</v>
+        <v>0.177</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3203</v>
+        <v>0.1522</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0704</v>
+        <v>-3.1091</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2614</v>
+        <v>-3.4345</v>
       </c>
       <c r="F12" t="n">
-        <v>0.191</v>
+        <v>0.3254</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6685</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4358</v>
+        <v>0.3971</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2284</v>
+        <v>0.0553</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2074</v>
+        <v>0.3418</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1418</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.246099999999998</v>
+        <v>10.7396</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.829899999999999</v>
+        <v>-0.3362000000000007</v>
       </c>
       <c r="F13" t="n">
         <v>11.0758</v>
@@ -1468,10 +1468,10 @@
         <v>19.7159</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7864000000000002</v>
+        <v>2.2799</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6854000000000002</v>
+        <v>0.8079999999999999</v>
       </c>
       <c r="U13" t="n">
         <v>1.4718</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8994</v>
+        <v>2.5175</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9956</v>
+        <v>3.5802</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0962</v>
+        <v>-1.0626</v>
       </c>
       <c r="G14" t="n">
         <v>-0.8588</v>
@@ -1546,13 +1546,13 @@
         <v>0.4639</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1678</v>
+        <v>1.786</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7799</v>
+        <v>1.3645</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3879</v>
+        <v>0.4215</v>
       </c>
       <c r="V14" t="n">
         <v>2.2862</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>A. BROOKS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.107</v>
+        <v>1.2113</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7825</v>
+        <v>3.1081</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6756</v>
+        <v>-1.8968</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8028</v>
+        <v>0.2549</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0911</v>
+        <v>0.7635</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8939</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4363</v>
+        <v>2.5854</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1176</v>
+        <v>2.8232</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3187</v>
+        <v>-0.2378</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6335</v>
+        <v>-2.3305</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2087</v>
+        <v>-2.0597</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4248</v>
+        <v>-0.2708</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9124</v>
+        <v>0.7244</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3462</v>
+        <v>0.3266</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5663</v>
+        <v>0.3978</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.3558</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BROOKS</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4205</v>
+        <v>0.7538</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7542</v>
+        <v>2.6646</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3337</v>
+        <v>-1.9108</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2549</v>
+        <v>0.8028</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7635</v>
+        <v>-1.0911</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5086000000000001</v>
+        <v>1.8939</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5854</v>
+        <v>2.4363</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8232</v>
+        <v>0.1176</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2378</v>
+        <v>2.3187</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3305</v>
+        <v>-1.6335</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.0597</v>
+        <v>-1.2087</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2708</v>
+        <v>-0.4248</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0663</v>
+        <v>0.5592</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0272</v>
+        <v>0.2282</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0391</v>
+        <v>0.331</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3558</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3558</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0431</v>
+        <v>-0.2607</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8906</v>
+        <v>-2.3624</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9337</v>
+        <v>2.1017</v>
       </c>
       <c r="G17" t="n">
         <v>1.1655</v>
@@ -1780,13 +1780,13 @@
         <v>2.3195</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1224</v>
+        <v>-1.4262</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5579</v>
+        <v>-1.0297</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5645</v>
+        <v>-0.3965</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. BOLMARO</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7069</v>
+        <v>-1.3434</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1142</v>
+        <v>-4.2898</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8211</v>
+        <v>2.9463</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2543</v>
+        <v>-1.4263</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9696</v>
+        <v>-1.1789</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2846</v>
+        <v>-0.2475</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3988</v>
+        <v>-1.2904</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7364</v>
+        <v>-0.5777</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6625</v>
+        <v>-0.7127</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1446</v>
+        <v>-0.1359</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7667</v>
+        <v>-0.6012</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3778</v>
+        <v>0.4653</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9432</v>
+        <v>-0.7057</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4832</v>
+        <v>-0.6798</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4599</v>
+        <v>-0.0259</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3943</v>
+        <v>0.7886</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>L. BOLMARO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.866</v>
+        <v>-1.3702</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.8795</v>
+        <v>0.3501</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0135</v>
+        <v>-1.7203</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4263</v>
+        <v>1.2543</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1789</v>
+        <v>0.9696</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2475</v>
+        <v>0.2846</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2904</v>
+        <v>3.3988</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5777</v>
+        <v>2.7364</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7127</v>
+        <v>0.6625</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1359</v>
+        <v>-2.1446</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6012</v>
+        <v>-1.7667</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4653</v>
+        <v>-0.3778</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2283</v>
+        <v>-0.6065</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2696</v>
+        <v>-0.2473</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0413</v>
+        <v>-0.3591</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7886</v>
+        <v>-0.3943</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7886</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7267</v>
+        <v>-1.9525</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.5874</v>
+        <v>-4.1156</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8606</v>
+        <v>2.1631</v>
       </c>
       <c r="G20" t="n">
         <v>-2.8487</v>
@@ -2014,13 +2014,13 @@
         <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.11</v>
+        <v>-1.3357</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4189</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.3886</v>
       </c>
       <c r="V20" t="n">
         <v>1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6289</v>
+        <v>-3.9149</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5268</v>
+        <v>-3.6448</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1021</v>
+        <v>-0.2701</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5891</v>
@@ -2092,13 +2092,13 @@
         <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2797</v>
+        <v>0.9937</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6449</v>
+        <v>0.5269</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6348</v>
+        <v>0.4668</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7874</v>
+        <v>-4.8869</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.8381</v>
+        <v>-6.3663</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0507</v>
+        <v>1.4794</v>
       </c>
       <c r="G22" t="n">
         <v>-3.2377</v>
@@ -2170,13 +2170,13 @@
         <v>2.5515</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6761</v>
+        <v>-0.7756</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4857</v>
+        <v>-1.0139</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8096</v>
+        <v>0.2383</v>
       </c>
       <c r="V22" t="n">
         <v>1.214</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.245899999999999</v>
+        <v>-9.245999999999999</v>
       </c>
       <c r="E23" t="n">
         <v>-11.0759</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8298</v>
+        <v>1.8299</v>
       </c>
       <c r="G23" t="n">
         <v>-5.4831</v>
@@ -2236,7 +2236,7 @@
         <v>-9.049300000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2024000000000002</v>
+        <v>0.2024</v>
       </c>
       <c r="P23" t="n">
         <v>-5.7988</v>
@@ -2248,13 +2248,13 @@
         <v>13.9171</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7863999999999992</v>
+        <v>-0.7863999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.4715</v>
+        <v>-1.4716</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6854000000000001</v>
+        <v>0.6853</v>
       </c>
       <c r="V23" t="n">
         <v>2.8223</v>
